--- a/HEN_NOC_Congestion_Playbook.xlsx
+++ b/HEN_NOC_Congestion_Playbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://huntconsolidatedinc-my.sharepoint.com/personal/wkight_huntenergy_com/Documents/Documents/Claude/Projects/HEN Congestion Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="11_F719340DD1292603DB29EB20D0964CC5F38AD59F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC86AACE-80EF-4E5E-A563-72DA3400CB29}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_F719340DD1292603DB29EB20D0964CC5F38AD59F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A28ED0C-6CD4-4483-AA1A-CB4ED8877533}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6855" yWindow="3120" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6165" yWindow="2415" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="⚠️ Disclaimer" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="642">
   <si>
     <t>⚡  HEN Real-Time Congestion Playbook</t>
   </si>
@@ -2149,6 +2149,9 @@
   </si>
   <si>
     <t>HE 10 saw the most shadow pricing but morning all around get best pricing. We see this congestion with low wind generation online, especially the west goin sub 3GW. Mostly completely correlated with west wind.</t>
+  </si>
+  <si>
+    <t>Newer congestion (start Nov 2025). Mostly see this congestion with cooler weather in the west creating higher load levels (9gw+) and wind sub 8GW. West wind is the major driver of this congestion. Common to see with west wind sub 3GW.</t>
   </si>
 </sst>
 </file>
@@ -2918,6 +2921,18 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2929,18 +2944,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3363,23 +3366,23 @@
       <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
     </row>
     <row r="3" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -3423,23 +3426,23 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="95"/>
     </row>
     <row r="5" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -3835,7 +3838,7 @@
         <v>90</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>91</v>
+        <v>641</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>92</v>
@@ -4061,23 +4064,23 @@
       <c r="M21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="92"/>
-      <c r="O22" s="92"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="96"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="96"/>
+      <c r="N22" s="96"/>
+      <c r="O22" s="96"/>
     </row>
     <row r="23" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -5436,23 +5439,23 @@
       <c r="M60" s="23"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="93" t="s">
+      <c r="A61" s="97" t="s">
         <v>299</v>
       </c>
-      <c r="B61" s="93"/>
-      <c r="C61" s="93"/>
-      <c r="D61" s="93"/>
-      <c r="E61" s="93"/>
-      <c r="F61" s="93"/>
-      <c r="G61" s="93"/>
-      <c r="H61" s="93"/>
-      <c r="I61" s="93"/>
-      <c r="J61" s="93"/>
-      <c r="K61" s="93"/>
-      <c r="L61" s="93"/>
-      <c r="M61" s="93"/>
-      <c r="N61" s="93"/>
-      <c r="O61" s="93"/>
+      <c r="B61" s="97"/>
+      <c r="C61" s="97"/>
+      <c r="D61" s="97"/>
+      <c r="E61" s="97"/>
+      <c r="F61" s="97"/>
+      <c r="G61" s="97"/>
+      <c r="H61" s="97"/>
+      <c r="I61" s="97"/>
+      <c r="J61" s="97"/>
+      <c r="K61" s="97"/>
+      <c r="L61" s="97"/>
+      <c r="M61" s="97"/>
+      <c r="N61" s="97"/>
+      <c r="O61" s="97"/>
     </row>
     <row r="62" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
@@ -7117,40 +7120,40 @@
       <c r="P1" s="89"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="90" t="s">
         <v>509</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="4" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="91" t="s">
         <v>510</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
       <c r="D4" s="35">
         <v>197</v>
       </c>
-      <c r="E4" s="96" t="s">
+      <c r="E4" s="92" t="s">
         <v>511</v>
       </c>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
     </row>
     <row r="6" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -10303,24 +10306,24 @@
       </c>
     </row>
     <row r="63" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="97" t="s">
+      <c r="A63" s="93" t="s">
         <v>527</v>
       </c>
-      <c r="B63" s="97"/>
-      <c r="C63" s="97"/>
-      <c r="D63" s="97"/>
-      <c r="E63" s="97"/>
-      <c r="F63" s="97"/>
-      <c r="G63" s="97"/>
-      <c r="H63" s="97"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="97"/>
-      <c r="K63" s="97"/>
-      <c r="L63" s="97"/>
-      <c r="M63" s="97"/>
-      <c r="N63" s="97"/>
-      <c r="O63" s="97"/>
-      <c r="P63" s="97"/>
+      <c r="B63" s="93"/>
+      <c r="C63" s="93"/>
+      <c r="D63" s="93"/>
+      <c r="E63" s="93"/>
+      <c r="F63" s="93"/>
+      <c r="G63" s="93"/>
+      <c r="H63" s="93"/>
+      <c r="I63" s="93"/>
+      <c r="J63" s="93"/>
+      <c r="K63" s="93"/>
+      <c r="L63" s="93"/>
+      <c r="M63" s="93"/>
+      <c r="N63" s="93"/>
+      <c r="O63" s="93"/>
+      <c r="P63" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -15539,24 +15542,24 @@
       <c r="P1" s="104"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="90" t="s">
         <v>585</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="3" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -19159,34 +19162,34 @@
       <c r="Z1" s="104"/>
     </row>
     <row r="2" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="90" t="s">
         <v>589</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="94"/>
-      <c r="S2" s="94"/>
-      <c r="T2" s="94"/>
-      <c r="U2" s="94"/>
-      <c r="V2" s="94"/>
-      <c r="W2" s="94"/>
-      <c r="X2" s="94"/>
-      <c r="Y2" s="94"/>
-      <c r="Z2" s="94"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="90"/>
+      <c r="R2" s="90"/>
+      <c r="S2" s="90"/>
+      <c r="T2" s="90"/>
+      <c r="U2" s="90"/>
+      <c r="V2" s="90"/>
+      <c r="W2" s="90"/>
+      <c r="X2" s="90"/>
+      <c r="Y2" s="90"/>
+      <c r="Z2" s="90"/>
     </row>
     <row r="3" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
